--- a/table/resources/sample/RobotAction_Bet.xlsx
+++ b/table/resources/sample/RobotAction_Bet.xlsx
@@ -216,25 +216,25 @@
     <t>ID</t>
   </si>
   <si>
-    <t>ActionID</t>
-  </si>
-  <si>
-    <t>GameID</t>
-  </si>
-  <si>
-    <t>BetAction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DelayTime </t>
-  </si>
-  <si>
-    <t>BettingArea</t>
-  </si>
-  <si>
-    <t>BetChips</t>
-  </si>
-  <si>
-    <t>NextTime</t>
+    <t>actionID</t>
+  </si>
+  <si>
+    <t>gameID</t>
+  </si>
+  <si>
+    <t>betAction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">delayTime </t>
+  </si>
+  <si>
+    <t>bettingArea</t>
+  </si>
+  <si>
+    <t>betChips</t>
+  </si>
+  <si>
+    <t>nextTime</t>
   </si>
   <si>
     <t>大额下注</t>
@@ -561,12 +561,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1729,7 +1729,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5">
-        <v>1</v>
+        <v>100001</v>
       </c>
       <c r="B5" s="4">
         <v>10099</v>
@@ -1761,7 +1761,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6">
-        <v>2</v>
+        <v>100002</v>
       </c>
       <c r="B6" s="4">
         <v>10099</v>
@@ -1793,7 +1793,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7">
-        <v>3</v>
+        <v>100003</v>
       </c>
       <c r="B7" s="4">
         <v>10099</v>
@@ -1825,7 +1825,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8">
-        <v>4</v>
+        <v>100004</v>
       </c>
       <c r="B8" s="4">
         <v>10075</v>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9">
-        <v>5</v>
+        <v>100005</v>
       </c>
       <c r="B9" s="4">
         <v>10075</v>
@@ -1889,7 +1889,7 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10">
-        <v>6</v>
+        <v>100006</v>
       </c>
       <c r="B10" s="4">
         <v>10075</v>
@@ -1921,7 +1921,7 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11">
-        <v>7</v>
+        <v>100007</v>
       </c>
       <c r="B11" s="4">
         <v>10050</v>
@@ -1953,7 +1953,7 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12">
-        <v>8</v>
+        <v>100008</v>
       </c>
       <c r="B12" s="4">
         <v>10050</v>
@@ -1985,7 +1985,7 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13">
-        <v>9</v>
+        <v>100009</v>
       </c>
       <c r="B13" s="4">
         <v>10050</v>
@@ -2017,7 +2017,7 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14">
-        <v>10</v>
+        <v>100010</v>
       </c>
       <c r="B14" s="4">
         <v>10025</v>
@@ -2049,7 +2049,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15">
-        <v>11</v>
+        <v>100011</v>
       </c>
       <c r="B15" s="4">
         <v>10025</v>
@@ -2081,7 +2081,7 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16">
-        <v>12</v>
+        <v>100012</v>
       </c>
       <c r="B16" s="4">
         <v>10025</v>
@@ -2113,7 +2113,7 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17">
-        <v>13</v>
+        <v>100013</v>
       </c>
       <c r="B17" s="4">
         <v>10001</v>
@@ -2145,7 +2145,7 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18">
-        <v>14</v>
+        <v>100014</v>
       </c>
       <c r="B18" s="4">
         <v>10001</v>
@@ -2177,7 +2177,7 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19">
-        <v>15</v>
+        <v>100015</v>
       </c>
       <c r="B19" s="4">
         <v>10001</v>
@@ -2209,7 +2209,7 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20">
-        <v>16</v>
+        <v>100016</v>
       </c>
       <c r="B20" s="4">
         <v>10099</v>
@@ -2241,7 +2241,7 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21">
-        <v>17</v>
+        <v>100017</v>
       </c>
       <c r="B21" s="4">
         <v>10099</v>
@@ -2273,7 +2273,7 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22">
-        <v>18</v>
+        <v>100018</v>
       </c>
       <c r="B22" s="4">
         <v>10099</v>
@@ -2305,7 +2305,7 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23">
-        <v>19</v>
+        <v>100019</v>
       </c>
       <c r="B23" s="4">
         <v>10075</v>
@@ -2337,7 +2337,7 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24">
-        <v>20</v>
+        <v>100020</v>
       </c>
       <c r="B24" s="4">
         <v>10075</v>
@@ -2369,7 +2369,7 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25">
-        <v>21</v>
+        <v>100021</v>
       </c>
       <c r="B25" s="4">
         <v>10075</v>
@@ -2401,7 +2401,7 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26">
-        <v>22</v>
+        <v>100022</v>
       </c>
       <c r="B26" s="4">
         <v>10050</v>
@@ -2433,7 +2433,7 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27">
-        <v>23</v>
+        <v>100023</v>
       </c>
       <c r="B27" s="4">
         <v>10050</v>
@@ -2465,7 +2465,7 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28">
-        <v>24</v>
+        <v>100024</v>
       </c>
       <c r="B28" s="4">
         <v>10050</v>
@@ -2497,7 +2497,7 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29">
-        <v>25</v>
+        <v>100025</v>
       </c>
       <c r="B29" s="4">
         <v>10025</v>
@@ -2529,7 +2529,7 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30">
-        <v>26</v>
+        <v>100026</v>
       </c>
       <c r="B30" s="4">
         <v>10025</v>
@@ -2561,7 +2561,7 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31">
-        <v>27</v>
+        <v>100027</v>
       </c>
       <c r="B31" s="4">
         <v>10025</v>
@@ -2593,7 +2593,7 @@
     </row>
     <row r="32" spans="1:10">
       <c r="A32">
-        <v>28</v>
+        <v>100028</v>
       </c>
       <c r="B32" s="4">
         <v>10001</v>
@@ -2625,7 +2625,7 @@
     </row>
     <row r="33" spans="1:10">
       <c r="A33">
-        <v>29</v>
+        <v>100029</v>
       </c>
       <c r="B33" s="4">
         <v>10001</v>
@@ -2657,7 +2657,7 @@
     </row>
     <row r="34" spans="1:10">
       <c r="A34">
-        <v>30</v>
+        <v>100030</v>
       </c>
       <c r="B34" s="4">
         <v>10001</v>
@@ -2689,7 +2689,7 @@
     </row>
     <row r="35" spans="1:10">
       <c r="A35">
-        <v>31</v>
+        <v>100031</v>
       </c>
       <c r="B35" s="4">
         <v>10099</v>
@@ -2721,7 +2721,7 @@
     </row>
     <row r="36" spans="1:10">
       <c r="A36">
-        <v>32</v>
+        <v>100032</v>
       </c>
       <c r="B36" s="4">
         <v>10099</v>
@@ -2753,7 +2753,7 @@
     </row>
     <row r="37" spans="1:10">
       <c r="A37">
-        <v>33</v>
+        <v>100033</v>
       </c>
       <c r="B37" s="4">
         <v>10099</v>
@@ -2785,7 +2785,7 @@
     </row>
     <row r="38" spans="1:10">
       <c r="A38">
-        <v>34</v>
+        <v>100034</v>
       </c>
       <c r="B38" s="4">
         <v>10075</v>
@@ -2817,7 +2817,7 @@
     </row>
     <row r="39" spans="1:10">
       <c r="A39">
-        <v>35</v>
+        <v>100035</v>
       </c>
       <c r="B39" s="4">
         <v>10075</v>
@@ -2849,7 +2849,7 @@
     </row>
     <row r="40" spans="1:10">
       <c r="A40">
-        <v>36</v>
+        <v>100036</v>
       </c>
       <c r="B40" s="4">
         <v>10075</v>
@@ -2881,7 +2881,7 @@
     </row>
     <row r="41" spans="1:10">
       <c r="A41">
-        <v>37</v>
+        <v>100037</v>
       </c>
       <c r="B41" s="4">
         <v>10050</v>
@@ -2913,7 +2913,7 @@
     </row>
     <row r="42" spans="1:10">
       <c r="A42">
-        <v>38</v>
+        <v>100038</v>
       </c>
       <c r="B42" s="4">
         <v>10050</v>
@@ -2945,7 +2945,7 @@
     </row>
     <row r="43" spans="1:10">
       <c r="A43">
-        <v>39</v>
+        <v>100039</v>
       </c>
       <c r="B43" s="4">
         <v>10050</v>
@@ -2977,7 +2977,7 @@
     </row>
     <row r="44" spans="1:10">
       <c r="A44">
-        <v>40</v>
+        <v>100040</v>
       </c>
       <c r="B44" s="4">
         <v>10025</v>
@@ -3009,7 +3009,7 @@
     </row>
     <row r="45" spans="1:10">
       <c r="A45">
-        <v>41</v>
+        <v>100041</v>
       </c>
       <c r="B45" s="4">
         <v>10025</v>
@@ -3041,7 +3041,7 @@
     </row>
     <row r="46" spans="1:10">
       <c r="A46">
-        <v>42</v>
+        <v>100042</v>
       </c>
       <c r="B46" s="4">
         <v>10025</v>
@@ -3073,7 +3073,7 @@
     </row>
     <row r="47" spans="1:10">
       <c r="A47">
-        <v>43</v>
+        <v>100043</v>
       </c>
       <c r="B47" s="4">
         <v>10001</v>
@@ -3105,7 +3105,7 @@
     </row>
     <row r="48" spans="1:10">
       <c r="A48">
-        <v>44</v>
+        <v>100044</v>
       </c>
       <c r="B48" s="4">
         <v>10001</v>
@@ -3137,7 +3137,7 @@
     </row>
     <row r="49" spans="1:10">
       <c r="A49">
-        <v>45</v>
+        <v>100045</v>
       </c>
       <c r="B49" s="4">
         <v>10001</v>
@@ -3169,7 +3169,7 @@
     </row>
     <row r="50" spans="1:10">
       <c r="A50">
-        <v>46</v>
+        <v>100046</v>
       </c>
       <c r="B50" s="4">
         <v>10099</v>
@@ -3201,7 +3201,7 @@
     </row>
     <row r="51" spans="1:10">
       <c r="A51">
-        <v>47</v>
+        <v>100047</v>
       </c>
       <c r="B51" s="4">
         <v>10099</v>
@@ -3233,7 +3233,7 @@
     </row>
     <row r="52" spans="1:10">
       <c r="A52">
-        <v>48</v>
+        <v>100048</v>
       </c>
       <c r="B52" s="4">
         <v>10099</v>
@@ -3265,7 +3265,7 @@
     </row>
     <row r="53" spans="1:10">
       <c r="A53">
-        <v>49</v>
+        <v>100049</v>
       </c>
       <c r="B53" s="4">
         <v>10075</v>
@@ -3297,7 +3297,7 @@
     </row>
     <row r="54" spans="1:10">
       <c r="A54">
-        <v>50</v>
+        <v>100050</v>
       </c>
       <c r="B54" s="4">
         <v>10075</v>
@@ -3329,7 +3329,7 @@
     </row>
     <row r="55" spans="1:10">
       <c r="A55">
-        <v>51</v>
+        <v>100051</v>
       </c>
       <c r="B55" s="4">
         <v>10075</v>
@@ -3361,7 +3361,7 @@
     </row>
     <row r="56" spans="1:10">
       <c r="A56">
-        <v>52</v>
+        <v>100052</v>
       </c>
       <c r="B56" s="4">
         <v>10050</v>
@@ -3393,7 +3393,7 @@
     </row>
     <row r="57" spans="1:10">
       <c r="A57">
-        <v>53</v>
+        <v>100053</v>
       </c>
       <c r="B57" s="4">
         <v>10050</v>
@@ -3425,7 +3425,7 @@
     </row>
     <row r="58" spans="1:10">
       <c r="A58">
-        <v>54</v>
+        <v>100054</v>
       </c>
       <c r="B58" s="4">
         <v>10050</v>
@@ -3457,7 +3457,7 @@
     </row>
     <row r="59" spans="1:10">
       <c r="A59">
-        <v>55</v>
+        <v>100055</v>
       </c>
       <c r="B59" s="4">
         <v>10025</v>
@@ -3489,7 +3489,7 @@
     </row>
     <row r="60" spans="1:10">
       <c r="A60">
-        <v>56</v>
+        <v>100056</v>
       </c>
       <c r="B60" s="4">
         <v>10025</v>
@@ -3521,7 +3521,7 @@
     </row>
     <row r="61" spans="1:10">
       <c r="A61">
-        <v>57</v>
+        <v>100057</v>
       </c>
       <c r="B61" s="4">
         <v>10025</v>
@@ -3553,7 +3553,7 @@
     </row>
     <row r="62" spans="1:10">
       <c r="A62">
-        <v>58</v>
+        <v>100058</v>
       </c>
       <c r="B62" s="4">
         <v>10001</v>
@@ -3585,7 +3585,7 @@
     </row>
     <row r="63" spans="1:10">
       <c r="A63">
-        <v>59</v>
+        <v>100059</v>
       </c>
       <c r="B63" s="4">
         <v>10001</v>
@@ -3617,7 +3617,7 @@
     </row>
     <row r="64" spans="1:10">
       <c r="A64">
-        <v>60</v>
+        <v>100060</v>
       </c>
       <c r="B64" s="4">
         <v>10001</v>
@@ -3649,7 +3649,7 @@
     </row>
     <row r="65" spans="1:10">
       <c r="A65">
-        <v>61</v>
+        <v>100061</v>
       </c>
       <c r="B65" s="4">
         <v>10099</v>
@@ -3681,7 +3681,7 @@
     </row>
     <row r="66" spans="1:10">
       <c r="A66">
-        <v>62</v>
+        <v>100062</v>
       </c>
       <c r="B66" s="4">
         <v>10099</v>
@@ -3713,7 +3713,7 @@
     </row>
     <row r="67" spans="1:10">
       <c r="A67">
-        <v>63</v>
+        <v>100063</v>
       </c>
       <c r="B67" s="4">
         <v>10099</v>
@@ -3745,7 +3745,7 @@
     </row>
     <row r="68" spans="1:10">
       <c r="A68">
-        <v>64</v>
+        <v>100064</v>
       </c>
       <c r="B68" s="4">
         <v>10075</v>
@@ -3777,7 +3777,7 @@
     </row>
     <row r="69" spans="1:10">
       <c r="A69">
-        <v>65</v>
+        <v>100065</v>
       </c>
       <c r="B69" s="4">
         <v>10075</v>
@@ -3809,7 +3809,7 @@
     </row>
     <row r="70" spans="1:10">
       <c r="A70">
-        <v>66</v>
+        <v>100066</v>
       </c>
       <c r="B70" s="4">
         <v>10075</v>
@@ -3841,7 +3841,7 @@
     </row>
     <row r="71" spans="1:10">
       <c r="A71">
-        <v>67</v>
+        <v>100067</v>
       </c>
       <c r="B71" s="4">
         <v>10050</v>
@@ -3873,7 +3873,7 @@
     </row>
     <row r="72" spans="1:10">
       <c r="A72">
-        <v>68</v>
+        <v>100068</v>
       </c>
       <c r="B72" s="4">
         <v>10050</v>
@@ -3905,7 +3905,7 @@
     </row>
     <row r="73" spans="1:10">
       <c r="A73">
-        <v>69</v>
+        <v>100069</v>
       </c>
       <c r="B73" s="4">
         <v>10050</v>
@@ -3937,7 +3937,7 @@
     </row>
     <row r="74" spans="1:10">
       <c r="A74">
-        <v>70</v>
+        <v>100070</v>
       </c>
       <c r="B74" s="4">
         <v>10025</v>
@@ -3969,7 +3969,7 @@
     </row>
     <row r="75" spans="1:10">
       <c r="A75">
-        <v>71</v>
+        <v>100071</v>
       </c>
       <c r="B75" s="4">
         <v>10025</v>
@@ -4001,7 +4001,7 @@
     </row>
     <row r="76" spans="1:10">
       <c r="A76">
-        <v>72</v>
+        <v>100072</v>
       </c>
       <c r="B76" s="4">
         <v>10025</v>
@@ -4033,7 +4033,7 @@
     </row>
     <row r="77" spans="1:10">
       <c r="A77">
-        <v>73</v>
+        <v>100073</v>
       </c>
       <c r="B77" s="4">
         <v>10001</v>
@@ -4065,7 +4065,7 @@
     </row>
     <row r="78" spans="1:10">
       <c r="A78">
-        <v>74</v>
+        <v>100074</v>
       </c>
       <c r="B78" s="4">
         <v>10001</v>
@@ -4097,7 +4097,7 @@
     </row>
     <row r="79" spans="1:10">
       <c r="A79">
-        <v>75</v>
+        <v>100075</v>
       </c>
       <c r="B79" s="4">
         <v>10001</v>
@@ -4129,7 +4129,7 @@
     </row>
     <row r="80" spans="1:10">
       <c r="A80">
-        <v>76</v>
+        <v>100076</v>
       </c>
       <c r="B80" s="4">
         <v>10099</v>
@@ -4161,7 +4161,7 @@
     </row>
     <row r="81" spans="1:10">
       <c r="A81">
-        <v>77</v>
+        <v>100077</v>
       </c>
       <c r="B81" s="4">
         <v>10099</v>
@@ -4193,7 +4193,7 @@
     </row>
     <row r="82" spans="1:10">
       <c r="A82">
-        <v>78</v>
+        <v>100078</v>
       </c>
       <c r="B82" s="4">
         <v>10099</v>
@@ -4225,7 +4225,7 @@
     </row>
     <row r="83" spans="1:10">
       <c r="A83">
-        <v>79</v>
+        <v>100079</v>
       </c>
       <c r="B83" s="4">
         <v>10075</v>
@@ -4257,7 +4257,7 @@
     </row>
     <row r="84" spans="1:10">
       <c r="A84">
-        <v>80</v>
+        <v>100080</v>
       </c>
       <c r="B84" s="4">
         <v>10075</v>
@@ -4289,7 +4289,7 @@
     </row>
     <row r="85" spans="1:10">
       <c r="A85">
-        <v>81</v>
+        <v>100081</v>
       </c>
       <c r="B85" s="4">
         <v>10075</v>
@@ -4321,7 +4321,7 @@
     </row>
     <row r="86" spans="1:10">
       <c r="A86">
-        <v>82</v>
+        <v>100082</v>
       </c>
       <c r="B86" s="4">
         <v>10050</v>
@@ -4353,7 +4353,7 @@
     </row>
     <row r="87" spans="1:10">
       <c r="A87">
-        <v>83</v>
+        <v>100083</v>
       </c>
       <c r="B87" s="4">
         <v>10050</v>
@@ -4385,7 +4385,7 @@
     </row>
     <row r="88" spans="1:10">
       <c r="A88">
-        <v>84</v>
+        <v>100084</v>
       </c>
       <c r="B88" s="4">
         <v>10050</v>
@@ -4417,7 +4417,7 @@
     </row>
     <row r="89" spans="1:10">
       <c r="A89">
-        <v>85</v>
+        <v>100085</v>
       </c>
       <c r="B89" s="4">
         <v>10025</v>
@@ -4449,7 +4449,7 @@
     </row>
     <row r="90" spans="1:10">
       <c r="A90">
-        <v>86</v>
+        <v>100086</v>
       </c>
       <c r="B90" s="4">
         <v>10025</v>
@@ -4481,7 +4481,7 @@
     </row>
     <row r="91" spans="1:10">
       <c r="A91">
-        <v>87</v>
+        <v>100087</v>
       </c>
       <c r="B91" s="4">
         <v>10025</v>
@@ -4513,7 +4513,7 @@
     </row>
     <row r="92" spans="1:10">
       <c r="A92">
-        <v>88</v>
+        <v>100088</v>
       </c>
       <c r="B92" s="4">
         <v>10001</v>
@@ -4545,7 +4545,7 @@
     </row>
     <row r="93" spans="1:10">
       <c r="A93">
-        <v>89</v>
+        <v>100089</v>
       </c>
       <c r="B93" s="4">
         <v>10001</v>
@@ -4577,7 +4577,7 @@
     </row>
     <row r="94" spans="1:10">
       <c r="A94">
-        <v>90</v>
+        <v>100090</v>
       </c>
       <c r="B94" s="4">
         <v>10001</v>
@@ -4609,7 +4609,7 @@
     </row>
     <row r="95" spans="1:10">
       <c r="A95">
-        <v>91</v>
+        <v>100091</v>
       </c>
       <c r="B95" s="4">
         <v>10099</v>
@@ -4641,7 +4641,7 @@
     </row>
     <row r="96" spans="1:10">
       <c r="A96">
-        <v>92</v>
+        <v>100092</v>
       </c>
       <c r="B96" s="4">
         <v>10099</v>
@@ -4673,7 +4673,7 @@
     </row>
     <row r="97" spans="1:10">
       <c r="A97">
-        <v>93</v>
+        <v>100093</v>
       </c>
       <c r="B97" s="4">
         <v>10099</v>
@@ -4705,7 +4705,7 @@
     </row>
     <row r="98" spans="1:10">
       <c r="A98">
-        <v>94</v>
+        <v>100094</v>
       </c>
       <c r="B98" s="4">
         <v>10075</v>
@@ -4737,7 +4737,7 @@
     </row>
     <row r="99" spans="1:10">
       <c r="A99">
-        <v>95</v>
+        <v>100095</v>
       </c>
       <c r="B99" s="4">
         <v>10075</v>
@@ -4769,7 +4769,7 @@
     </row>
     <row r="100" spans="1:10">
       <c r="A100">
-        <v>96</v>
+        <v>100096</v>
       </c>
       <c r="B100" s="4">
         <v>10075</v>
@@ -4801,7 +4801,7 @@
     </row>
     <row r="101" spans="1:10">
       <c r="A101">
-        <v>97</v>
+        <v>100097</v>
       </c>
       <c r="B101" s="4">
         <v>10050</v>
@@ -4833,7 +4833,7 @@
     </row>
     <row r="102" spans="1:10">
       <c r="A102">
-        <v>98</v>
+        <v>100098</v>
       </c>
       <c r="B102" s="4">
         <v>10050</v>
@@ -4865,7 +4865,7 @@
     </row>
     <row r="103" spans="1:10">
       <c r="A103">
-        <v>99</v>
+        <v>100099</v>
       </c>
       <c r="B103" s="4">
         <v>10050</v>
@@ -4897,7 +4897,7 @@
     </row>
     <row r="104" spans="1:10">
       <c r="A104">
-        <v>100</v>
+        <v>100100</v>
       </c>
       <c r="B104" s="4">
         <v>10025</v>
@@ -4929,7 +4929,7 @@
     </row>
     <row r="105" spans="1:10">
       <c r="A105">
-        <v>101</v>
+        <v>100101</v>
       </c>
       <c r="B105" s="4">
         <v>10025</v>
@@ -4961,7 +4961,7 @@
     </row>
     <row r="106" spans="1:10">
       <c r="A106">
-        <v>102</v>
+        <v>100102</v>
       </c>
       <c r="B106" s="4">
         <v>10025</v>
@@ -4993,7 +4993,7 @@
     </row>
     <row r="107" spans="1:10">
       <c r="A107">
-        <v>103</v>
+        <v>100103</v>
       </c>
       <c r="B107" s="4">
         <v>10001</v>
@@ -5025,7 +5025,7 @@
     </row>
     <row r="108" spans="1:10">
       <c r="A108">
-        <v>104</v>
+        <v>100104</v>
       </c>
       <c r="B108" s="4">
         <v>10001</v>
@@ -5057,7 +5057,7 @@
     </row>
     <row r="109" spans="1:10">
       <c r="A109">
-        <v>105</v>
+        <v>100105</v>
       </c>
       <c r="B109" s="4">
         <v>10001</v>
@@ -5089,7 +5089,7 @@
     </row>
     <row r="110" spans="1:10">
       <c r="A110">
-        <v>106</v>
+        <v>100106</v>
       </c>
       <c r="B110" s="4">
         <v>10099</v>
@@ -5121,7 +5121,7 @@
     </row>
     <row r="111" spans="1:10">
       <c r="A111">
-        <v>107</v>
+        <v>100107</v>
       </c>
       <c r="B111" s="4">
         <v>10099</v>
@@ -5153,7 +5153,7 @@
     </row>
     <row r="112" spans="1:10">
       <c r="A112">
-        <v>108</v>
+        <v>100108</v>
       </c>
       <c r="B112" s="4">
         <v>10099</v>
@@ -5185,7 +5185,7 @@
     </row>
     <row r="113" spans="1:10">
       <c r="A113">
-        <v>109</v>
+        <v>100109</v>
       </c>
       <c r="B113" s="4">
         <v>10075</v>
@@ -5217,7 +5217,7 @@
     </row>
     <row r="114" spans="1:10">
       <c r="A114">
-        <v>110</v>
+        <v>100110</v>
       </c>
       <c r="B114" s="4">
         <v>10075</v>
@@ -5249,7 +5249,7 @@
     </row>
     <row r="115" spans="1:10">
       <c r="A115">
-        <v>111</v>
+        <v>100111</v>
       </c>
       <c r="B115" s="4">
         <v>10075</v>
@@ -5281,7 +5281,7 @@
     </row>
     <row r="116" spans="1:10">
       <c r="A116">
-        <v>112</v>
+        <v>100112</v>
       </c>
       <c r="B116" s="4">
         <v>10050</v>
@@ -5313,7 +5313,7 @@
     </row>
     <row r="117" spans="1:10">
       <c r="A117">
-        <v>113</v>
+        <v>100113</v>
       </c>
       <c r="B117" s="4">
         <v>10050</v>
@@ -5345,7 +5345,7 @@
     </row>
     <row r="118" spans="1:10">
       <c r="A118">
-        <v>114</v>
+        <v>100114</v>
       </c>
       <c r="B118" s="4">
         <v>10050</v>
@@ -5377,7 +5377,7 @@
     </row>
     <row r="119" spans="1:10">
       <c r="A119">
-        <v>115</v>
+        <v>100115</v>
       </c>
       <c r="B119" s="4">
         <v>10025</v>
@@ -5409,7 +5409,7 @@
     </row>
     <row r="120" spans="1:10">
       <c r="A120">
-        <v>116</v>
+        <v>100116</v>
       </c>
       <c r="B120" s="4">
         <v>10025</v>
@@ -5441,7 +5441,7 @@
     </row>
     <row r="121" spans="1:10">
       <c r="A121">
-        <v>117</v>
+        <v>100117</v>
       </c>
       <c r="B121" s="4">
         <v>10025</v>
@@ -5473,7 +5473,7 @@
     </row>
     <row r="122" spans="1:10">
       <c r="A122">
-        <v>118</v>
+        <v>100118</v>
       </c>
       <c r="B122" s="4">
         <v>10001</v>
@@ -5505,7 +5505,7 @@
     </row>
     <row r="123" spans="1:10">
       <c r="A123">
-        <v>119</v>
+        <v>100119</v>
       </c>
       <c r="B123" s="4">
         <v>10001</v>
@@ -5537,7 +5537,7 @@
     </row>
     <row r="124" spans="1:10">
       <c r="A124">
-        <v>120</v>
+        <v>100120</v>
       </c>
       <c r="B124" s="4">
         <v>10001</v>
@@ -5569,7 +5569,7 @@
     </row>
     <row r="125" spans="1:10">
       <c r="A125">
-        <v>121</v>
+        <v>100121</v>
       </c>
       <c r="B125" s="4">
         <v>10099</v>
@@ -5601,7 +5601,7 @@
     </row>
     <row r="126" spans="1:10">
       <c r="A126">
-        <v>122</v>
+        <v>100122</v>
       </c>
       <c r="B126" s="4">
         <v>10099</v>
@@ -5633,7 +5633,7 @@
     </row>
     <row r="127" spans="1:10">
       <c r="A127">
-        <v>123</v>
+        <v>100123</v>
       </c>
       <c r="B127" s="4">
         <v>10099</v>
@@ -5665,7 +5665,7 @@
     </row>
     <row r="128" spans="1:10">
       <c r="A128">
-        <v>124</v>
+        <v>100124</v>
       </c>
       <c r="B128" s="4">
         <v>10075</v>
@@ -5697,7 +5697,7 @@
     </row>
     <row r="129" spans="1:10">
       <c r="A129">
-        <v>125</v>
+        <v>100125</v>
       </c>
       <c r="B129" s="4">
         <v>10075</v>
@@ -5729,7 +5729,7 @@
     </row>
     <row r="130" spans="1:10">
       <c r="A130">
-        <v>126</v>
+        <v>100126</v>
       </c>
       <c r="B130" s="4">
         <v>10075</v>
@@ -5761,7 +5761,7 @@
     </row>
     <row r="131" spans="1:10">
       <c r="A131">
-        <v>127</v>
+        <v>100127</v>
       </c>
       <c r="B131" s="4">
         <v>10050</v>
@@ -5793,7 +5793,7 @@
     </row>
     <row r="132" spans="1:10">
       <c r="A132">
-        <v>128</v>
+        <v>100128</v>
       </c>
       <c r="B132" s="4">
         <v>10050</v>
@@ -5825,7 +5825,7 @@
     </row>
     <row r="133" spans="1:10">
       <c r="A133">
-        <v>129</v>
+        <v>100129</v>
       </c>
       <c r="B133" s="4">
         <v>10050</v>
@@ -5857,7 +5857,7 @@
     </row>
     <row r="134" spans="1:10">
       <c r="A134">
-        <v>130</v>
+        <v>100130</v>
       </c>
       <c r="B134" s="4">
         <v>10025</v>
@@ -5889,7 +5889,7 @@
     </row>
     <row r="135" spans="1:10">
       <c r="A135">
-        <v>131</v>
+        <v>100131</v>
       </c>
       <c r="B135" s="4">
         <v>10025</v>
@@ -5921,7 +5921,7 @@
     </row>
     <row r="136" spans="1:10">
       <c r="A136">
-        <v>132</v>
+        <v>100132</v>
       </c>
       <c r="B136" s="4">
         <v>10025</v>
@@ -5953,7 +5953,7 @@
     </row>
     <row r="137" spans="1:10">
       <c r="A137">
-        <v>133</v>
+        <v>100133</v>
       </c>
       <c r="B137" s="4">
         <v>10001</v>
@@ -5985,7 +5985,7 @@
     </row>
     <row r="138" spans="1:10">
       <c r="A138">
-        <v>134</v>
+        <v>100134</v>
       </c>
       <c r="B138" s="4">
         <v>10001</v>
@@ -6017,7 +6017,7 @@
     </row>
     <row r="139" spans="1:10">
       <c r="A139">
-        <v>135</v>
+        <v>100135</v>
       </c>
       <c r="B139" s="4">
         <v>10001</v>

--- a/table/resources/sample/RobotAction_Bet.xlsx
+++ b/table/resources/sample/RobotAction_Bet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BetRobot" sheetId="1" r:id="rId1"/>
@@ -178,7 +178,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="69">
   <si>
     <t>序列</t>
   </si>
@@ -1062,7 +1062,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1098,6 +1098,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1625,7 +1628,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J139"/>
+  <dimension ref="A1:J154"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="4" width="12.875" style="1" customWidth="1"/>
@@ -6047,6 +6050,486 @@
         <v>32</v>
       </c>
     </row>
+    <row r="140" spans="1:10">
+      <c r="A140">
+        <v>100136</v>
+      </c>
+      <c r="B140" s="4">
+        <v>10099</v>
+      </c>
+      <c r="C140" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D140" s="13">
+        <v>20060010</v>
+      </c>
+      <c r="E140" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F140">
+        <v>9000</v>
+      </c>
+      <c r="G140" t="s">
+        <v>21</v>
+      </c>
+      <c r="H140" t="s">
+        <v>54</v>
+      </c>
+      <c r="I140" t="s">
+        <v>23</v>
+      </c>
+      <c r="J140" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10">
+      <c r="A141">
+        <v>100137</v>
+      </c>
+      <c r="B141" s="4">
+        <v>10099</v>
+      </c>
+      <c r="C141" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D141" s="13">
+        <v>20060011</v>
+      </c>
+      <c r="E141" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F141">
+        <v>9000</v>
+      </c>
+      <c r="G141" t="s">
+        <v>21</v>
+      </c>
+      <c r="H141" t="s">
+        <v>54</v>
+      </c>
+      <c r="I141" t="s">
+        <v>23</v>
+      </c>
+      <c r="J141" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10">
+      <c r="A142">
+        <v>100138</v>
+      </c>
+      <c r="B142" s="4">
+        <v>10099</v>
+      </c>
+      <c r="C142" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D142" s="13">
+        <v>20060012</v>
+      </c>
+      <c r="E142" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F142">
+        <v>9000</v>
+      </c>
+      <c r="G142" t="s">
+        <v>21</v>
+      </c>
+      <c r="H142" t="s">
+        <v>54</v>
+      </c>
+      <c r="I142" t="s">
+        <v>23</v>
+      </c>
+      <c r="J142" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10">
+      <c r="A143">
+        <v>100139</v>
+      </c>
+      <c r="B143" s="4">
+        <v>10075</v>
+      </c>
+      <c r="C143" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D143" s="13">
+        <v>20060010</v>
+      </c>
+      <c r="E143" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F143">
+        <v>7000</v>
+      </c>
+      <c r="G143" t="s">
+        <v>28</v>
+      </c>
+      <c r="H143" t="s">
+        <v>54</v>
+      </c>
+      <c r="I143" t="s">
+        <v>23</v>
+      </c>
+      <c r="J143" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10">
+      <c r="A144">
+        <v>100140</v>
+      </c>
+      <c r="B144" s="4">
+        <v>10075</v>
+      </c>
+      <c r="C144" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D144" s="13">
+        <v>20060011</v>
+      </c>
+      <c r="E144" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F144">
+        <v>7000</v>
+      </c>
+      <c r="G144" t="s">
+        <v>28</v>
+      </c>
+      <c r="H144" t="s">
+        <v>54</v>
+      </c>
+      <c r="I144" t="s">
+        <v>23</v>
+      </c>
+      <c r="J144" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10">
+      <c r="A145">
+        <v>100141</v>
+      </c>
+      <c r="B145" s="4">
+        <v>10075</v>
+      </c>
+      <c r="C145" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D145" s="13">
+        <v>20060012</v>
+      </c>
+      <c r="E145" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F145">
+        <v>7000</v>
+      </c>
+      <c r="G145" t="s">
+        <v>28</v>
+      </c>
+      <c r="H145" t="s">
+        <v>54</v>
+      </c>
+      <c r="I145" t="s">
+        <v>23</v>
+      </c>
+      <c r="J145" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10">
+      <c r="A146">
+        <v>100142</v>
+      </c>
+      <c r="B146" s="4">
+        <v>10050</v>
+      </c>
+      <c r="C146" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D146" s="13">
+        <v>20060010</v>
+      </c>
+      <c r="E146" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F146">
+        <v>5000</v>
+      </c>
+      <c r="G146" t="s">
+        <v>31</v>
+      </c>
+      <c r="H146" t="s">
+        <v>54</v>
+      </c>
+      <c r="I146" t="s">
+        <v>23</v>
+      </c>
+      <c r="J146" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10">
+      <c r="A147">
+        <v>100143</v>
+      </c>
+      <c r="B147" s="4">
+        <v>10050</v>
+      </c>
+      <c r="C147" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D147" s="13">
+        <v>20060011</v>
+      </c>
+      <c r="E147" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F147">
+        <v>5000</v>
+      </c>
+      <c r="G147" t="s">
+        <v>31</v>
+      </c>
+      <c r="H147" t="s">
+        <v>54</v>
+      </c>
+      <c r="I147" t="s">
+        <v>23</v>
+      </c>
+      <c r="J147" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10">
+      <c r="A148">
+        <v>100144</v>
+      </c>
+      <c r="B148" s="4">
+        <v>10050</v>
+      </c>
+      <c r="C148" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D148" s="13">
+        <v>20060012</v>
+      </c>
+      <c r="E148" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F148">
+        <v>5000</v>
+      </c>
+      <c r="G148" t="s">
+        <v>31</v>
+      </c>
+      <c r="H148" t="s">
+        <v>54</v>
+      </c>
+      <c r="I148" t="s">
+        <v>23</v>
+      </c>
+      <c r="J148" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10">
+      <c r="A149">
+        <v>100145</v>
+      </c>
+      <c r="B149" s="4">
+        <v>10025</v>
+      </c>
+      <c r="C149" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D149" s="13">
+        <v>20060010</v>
+      </c>
+      <c r="E149" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F149">
+        <v>4000</v>
+      </c>
+      <c r="G149" t="s">
+        <v>34</v>
+      </c>
+      <c r="H149" t="s">
+        <v>54</v>
+      </c>
+      <c r="I149" t="s">
+        <v>23</v>
+      </c>
+      <c r="J149" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10">
+      <c r="A150">
+        <v>100146</v>
+      </c>
+      <c r="B150" s="4">
+        <v>10025</v>
+      </c>
+      <c r="C150" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D150" s="13">
+        <v>20060011</v>
+      </c>
+      <c r="E150" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F150">
+        <v>4000</v>
+      </c>
+      <c r="G150" t="s">
+        <v>34</v>
+      </c>
+      <c r="H150" t="s">
+        <v>54</v>
+      </c>
+      <c r="I150" t="s">
+        <v>23</v>
+      </c>
+      <c r="J150" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10">
+      <c r="A151">
+        <v>100147</v>
+      </c>
+      <c r="B151" s="4">
+        <v>10025</v>
+      </c>
+      <c r="C151" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D151" s="13">
+        <v>20060012</v>
+      </c>
+      <c r="E151" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F151">
+        <v>4000</v>
+      </c>
+      <c r="G151" t="s">
+        <v>34</v>
+      </c>
+      <c r="H151" t="s">
+        <v>54</v>
+      </c>
+      <c r="I151" t="s">
+        <v>23</v>
+      </c>
+      <c r="J151" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10">
+      <c r="A152">
+        <v>100148</v>
+      </c>
+      <c r="B152" s="4">
+        <v>10001</v>
+      </c>
+      <c r="C152" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D152" s="13">
+        <v>20060010</v>
+      </c>
+      <c r="E152" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F152">
+        <v>2000</v>
+      </c>
+      <c r="G152" t="s">
+        <v>36</v>
+      </c>
+      <c r="H152" t="s">
+        <v>54</v>
+      </c>
+      <c r="I152" t="s">
+        <v>23</v>
+      </c>
+      <c r="J152" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10">
+      <c r="A153">
+        <v>100149</v>
+      </c>
+      <c r="B153" s="4">
+        <v>10001</v>
+      </c>
+      <c r="C153" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D153" s="13">
+        <v>20060011</v>
+      </c>
+      <c r="E153" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F153">
+        <v>2000</v>
+      </c>
+      <c r="G153" t="s">
+        <v>36</v>
+      </c>
+      <c r="H153" t="s">
+        <v>54</v>
+      </c>
+      <c r="I153" t="s">
+        <v>23</v>
+      </c>
+      <c r="J153" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10">
+      <c r="A154">
+        <v>100150</v>
+      </c>
+      <c r="B154" s="4">
+        <v>10001</v>
+      </c>
+      <c r="C154" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D154" s="13">
+        <v>20060012</v>
+      </c>
+      <c r="E154" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F154">
+        <v>2000</v>
+      </c>
+      <c r="G154" t="s">
+        <v>36</v>
+      </c>
+      <c r="H154" t="s">
+        <v>54</v>
+      </c>
+      <c r="I154" t="s">
+        <v>23</v>
+      </c>
+      <c r="J154" t="s">
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/table/resources/sample/RobotAction_Bet.xlsx
+++ b/table/resources/sample/RobotAction_Bet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BetRobot" sheetId="1" r:id="rId1"/>
@@ -178,7 +178,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="69">
   <si>
     <t>序列</t>
   </si>
@@ -1062,7 +1062,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1098,9 +1098,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1628,7 +1625,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J154"/>
+  <dimension ref="A1:J139"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="4" width="12.875" style="1" customWidth="1"/>
@@ -6050,486 +6047,6 @@
         <v>32</v>
       </c>
     </row>
-    <row r="140" spans="1:10">
-      <c r="A140">
-        <v>100136</v>
-      </c>
-      <c r="B140" s="4">
-        <v>10099</v>
-      </c>
-      <c r="C140" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D140" s="13">
-        <v>20060010</v>
-      </c>
-      <c r="E140" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="F140">
-        <v>9000</v>
-      </c>
-      <c r="G140" t="s">
-        <v>21</v>
-      </c>
-      <c r="H140" t="s">
-        <v>54</v>
-      </c>
-      <c r="I140" t="s">
-        <v>23</v>
-      </c>
-      <c r="J140" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="141" spans="1:10">
-      <c r="A141">
-        <v>100137</v>
-      </c>
-      <c r="B141" s="4">
-        <v>10099</v>
-      </c>
-      <c r="C141" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D141" s="13">
-        <v>20060011</v>
-      </c>
-      <c r="E141" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="F141">
-        <v>9000</v>
-      </c>
-      <c r="G141" t="s">
-        <v>21</v>
-      </c>
-      <c r="H141" t="s">
-        <v>54</v>
-      </c>
-      <c r="I141" t="s">
-        <v>23</v>
-      </c>
-      <c r="J141" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="142" spans="1:10">
-      <c r="A142">
-        <v>100138</v>
-      </c>
-      <c r="B142" s="4">
-        <v>10099</v>
-      </c>
-      <c r="C142" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D142" s="13">
-        <v>20060012</v>
-      </c>
-      <c r="E142" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="F142">
-        <v>9000</v>
-      </c>
-      <c r="G142" t="s">
-        <v>21</v>
-      </c>
-      <c r="H142" t="s">
-        <v>54</v>
-      </c>
-      <c r="I142" t="s">
-        <v>23</v>
-      </c>
-      <c r="J142" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="143" spans="1:10">
-      <c r="A143">
-        <v>100139</v>
-      </c>
-      <c r="B143" s="4">
-        <v>10075</v>
-      </c>
-      <c r="C143" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D143" s="13">
-        <v>20060010</v>
-      </c>
-      <c r="E143" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="F143">
-        <v>7000</v>
-      </c>
-      <c r="G143" t="s">
-        <v>28</v>
-      </c>
-      <c r="H143" t="s">
-        <v>54</v>
-      </c>
-      <c r="I143" t="s">
-        <v>23</v>
-      </c>
-      <c r="J143" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="144" spans="1:10">
-      <c r="A144">
-        <v>100140</v>
-      </c>
-      <c r="B144" s="4">
-        <v>10075</v>
-      </c>
-      <c r="C144" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D144" s="13">
-        <v>20060011</v>
-      </c>
-      <c r="E144" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="F144">
-        <v>7000</v>
-      </c>
-      <c r="G144" t="s">
-        <v>28</v>
-      </c>
-      <c r="H144" t="s">
-        <v>54</v>
-      </c>
-      <c r="I144" t="s">
-        <v>23</v>
-      </c>
-      <c r="J144" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="145" spans="1:10">
-      <c r="A145">
-        <v>100141</v>
-      </c>
-      <c r="B145" s="4">
-        <v>10075</v>
-      </c>
-      <c r="C145" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D145" s="13">
-        <v>20060012</v>
-      </c>
-      <c r="E145" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="F145">
-        <v>7000</v>
-      </c>
-      <c r="G145" t="s">
-        <v>28</v>
-      </c>
-      <c r="H145" t="s">
-        <v>54</v>
-      </c>
-      <c r="I145" t="s">
-        <v>23</v>
-      </c>
-      <c r="J145" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="146" spans="1:10">
-      <c r="A146">
-        <v>100142</v>
-      </c>
-      <c r="B146" s="4">
-        <v>10050</v>
-      </c>
-      <c r="C146" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D146" s="13">
-        <v>20060010</v>
-      </c>
-      <c r="E146" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="F146">
-        <v>5000</v>
-      </c>
-      <c r="G146" t="s">
-        <v>31</v>
-      </c>
-      <c r="H146" t="s">
-        <v>54</v>
-      </c>
-      <c r="I146" t="s">
-        <v>23</v>
-      </c>
-      <c r="J146" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="147" spans="1:10">
-      <c r="A147">
-        <v>100143</v>
-      </c>
-      <c r="B147" s="4">
-        <v>10050</v>
-      </c>
-      <c r="C147" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D147" s="13">
-        <v>20060011</v>
-      </c>
-      <c r="E147" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="F147">
-        <v>5000</v>
-      </c>
-      <c r="G147" t="s">
-        <v>31</v>
-      </c>
-      <c r="H147" t="s">
-        <v>54</v>
-      </c>
-      <c r="I147" t="s">
-        <v>23</v>
-      </c>
-      <c r="J147" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="148" spans="1:10">
-      <c r="A148">
-        <v>100144</v>
-      </c>
-      <c r="B148" s="4">
-        <v>10050</v>
-      </c>
-      <c r="C148" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D148" s="13">
-        <v>20060012</v>
-      </c>
-      <c r="E148" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="F148">
-        <v>5000</v>
-      </c>
-      <c r="G148" t="s">
-        <v>31</v>
-      </c>
-      <c r="H148" t="s">
-        <v>54</v>
-      </c>
-      <c r="I148" t="s">
-        <v>23</v>
-      </c>
-      <c r="J148" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="149" spans="1:10">
-      <c r="A149">
-        <v>100145</v>
-      </c>
-      <c r="B149" s="4">
-        <v>10025</v>
-      </c>
-      <c r="C149" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D149" s="13">
-        <v>20060010</v>
-      </c>
-      <c r="E149" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="F149">
-        <v>4000</v>
-      </c>
-      <c r="G149" t="s">
-        <v>34</v>
-      </c>
-      <c r="H149" t="s">
-        <v>54</v>
-      </c>
-      <c r="I149" t="s">
-        <v>23</v>
-      </c>
-      <c r="J149" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="150" spans="1:10">
-      <c r="A150">
-        <v>100146</v>
-      </c>
-      <c r="B150" s="4">
-        <v>10025</v>
-      </c>
-      <c r="C150" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D150" s="13">
-        <v>20060011</v>
-      </c>
-      <c r="E150" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="F150">
-        <v>4000</v>
-      </c>
-      <c r="G150" t="s">
-        <v>34</v>
-      </c>
-      <c r="H150" t="s">
-        <v>54</v>
-      </c>
-      <c r="I150" t="s">
-        <v>23</v>
-      </c>
-      <c r="J150" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="151" spans="1:10">
-      <c r="A151">
-        <v>100147</v>
-      </c>
-      <c r="B151" s="4">
-        <v>10025</v>
-      </c>
-      <c r="C151" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D151" s="13">
-        <v>20060012</v>
-      </c>
-      <c r="E151" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="F151">
-        <v>4000</v>
-      </c>
-      <c r="G151" t="s">
-        <v>34</v>
-      </c>
-      <c r="H151" t="s">
-        <v>54</v>
-      </c>
-      <c r="I151" t="s">
-        <v>23</v>
-      </c>
-      <c r="J151" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="152" spans="1:10">
-      <c r="A152">
-        <v>100148</v>
-      </c>
-      <c r="B152" s="4">
-        <v>10001</v>
-      </c>
-      <c r="C152" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D152" s="13">
-        <v>20060010</v>
-      </c>
-      <c r="E152" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="F152">
-        <v>2000</v>
-      </c>
-      <c r="G152" t="s">
-        <v>36</v>
-      </c>
-      <c r="H152" t="s">
-        <v>54</v>
-      </c>
-      <c r="I152" t="s">
-        <v>23</v>
-      </c>
-      <c r="J152" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="153" spans="1:10">
-      <c r="A153">
-        <v>100149</v>
-      </c>
-      <c r="B153" s="4">
-        <v>10001</v>
-      </c>
-      <c r="C153" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D153" s="13">
-        <v>20060011</v>
-      </c>
-      <c r="E153" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="F153">
-        <v>2000</v>
-      </c>
-      <c r="G153" t="s">
-        <v>36</v>
-      </c>
-      <c r="H153" t="s">
-        <v>54</v>
-      </c>
-      <c r="I153" t="s">
-        <v>23</v>
-      </c>
-      <c r="J153" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="154" spans="1:10">
-      <c r="A154">
-        <v>100150</v>
-      </c>
-      <c r="B154" s="4">
-        <v>10001</v>
-      </c>
-      <c r="C154" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D154" s="13">
-        <v>20060012</v>
-      </c>
-      <c r="E154" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="F154">
-        <v>2000</v>
-      </c>
-      <c r="G154" t="s">
-        <v>36</v>
-      </c>
-      <c r="H154" t="s">
-        <v>54</v>
-      </c>
-      <c r="I154" t="s">
-        <v>23</v>
-      </c>
-      <c r="J154" t="s">
-        <v>32</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/table/resources/sample/RobotAction_Bet.xlsx
+++ b/table/resources/sample/RobotAction_Bet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BetRobot" sheetId="1" r:id="rId1"/>
@@ -178,7 +178,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="73">
   <si>
     <t>序列</t>
   </si>
@@ -385,6 +385,18 @@
   </si>
   <si>
     <t>鱼虾蟹高级场</t>
+  </si>
+  <si>
+    <t>俄罗斯轮盘基础场</t>
+  </si>
+  <si>
+    <t>64,20120001;64,20120002;64,20120003;64,20120004;64,20120005;64,20120006;64,20120007;64,20120008;64,20120009;64,20120010;64,20120011;64,20120012;64,20120013;64,20120014;64,20120015;64,20120016;64,20120017;64,20120018;64,20120019;64,20120020;64,20120021;64,20120022;64,20120023;64,20120024;64,20120025;64,20120026;64,20120027;64,20120028;64,20120029;64,20120030;64,20120031;64,20120032;64,20120033;64,20120034;64,20120035;64,20120036;64,20120037;64,20120038;64,20120039;64,20120040;64,20120041;64,20120042;64,20120043;64,20120044;64,20120045;64,20120046;64,20120047;64,20120048;64,20120049;64,20120050;64,20120051;64,20120052;64,20120053;64,20120054;64,20120055;64,20120056;64,20120057;64,20120058;64,20120059;64,20120060;64,20120061;64,20120062;64,20120063;64,20120064;64,20120065;64,20120066;64,20120067;64,20120068;64,20120069;64,20120070;64,20120071;64,20120072;64,20120073;64,20120074;64,20120075;64,20120076;64,20120077;64,20120078;64,20120079;64,20120080;64,20120081;64,20120082;64,20120083;64,20120084;64,20120085;64,20120086;64,20120087;64,20120088;64,20120089;64,20120090;64,20120091;64,20120092;64,20120093;64,20120094;64,20120095;64,20120096;64,20120097;64,20120098;64,20120099;64,20120100;64,20120101;64,20120102;64,20120103;64,20120104;64,20120105;64,20120106;64,20120107;64,20120108;64,20120109;64,20120110;64,20120111;64,20120112;64,20120113;64,20120114;64,20120115;64,20120116;64,20120117;64,20120118;64,20120119;64,20120120;64,20120121;64,20120122;64,20120123;64,20120124;64,20120125;64,20120126;64,20120127;64,20120128;64,20120129;64,20120130;64,20120131;64,20120132;64,20120133;64,20120134;64,20120135;64,20120136;64,20120137;64,20120138;64,20120139;64,20120140;64,20120141;64,20120142;64,20120143;64,20120144;64,20120145;64,20120146;64,20120147;64,20120148;64,20120149;64,20120150;64,20120151;64,20120152;64,20120153;64,20120154;64,20120155;64,20120156</t>
+  </si>
+  <si>
+    <t>俄罗斯轮盘中级场</t>
+  </si>
+  <si>
+    <t>俄罗斯轮盘高级场</t>
   </si>
 </sst>
 </file>
@@ -572,7 +584,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -618,6 +630,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -915,7 +933,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
@@ -938,7 +956,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -962,16 +980,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -980,89 +998,90 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1100,8 +1119,11 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
     <cellStyle name="货币" xfId="2" builtinId="4"/>
@@ -1151,6 +1173,7 @@
     <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 2 2" xfId="49"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
@@ -1625,7 +1648,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J139"/>
+  <dimension ref="A1:J154"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="4" width="12.875" style="1" customWidth="1"/>
@@ -1721,7 +1744,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="2:5">
+    <row r="4" spans="1:10">
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -6044,6 +6067,486 @@
         <v>23</v>
       </c>
       <c r="J139" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10">
+      <c r="A140">
+        <v>100136</v>
+      </c>
+      <c r="B140" s="4">
+        <v>10099</v>
+      </c>
+      <c r="C140" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D140" s="5">
+        <v>2012001</v>
+      </c>
+      <c r="E140" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="F140">
+        <v>9000</v>
+      </c>
+      <c r="G140" t="s">
+        <v>21</v>
+      </c>
+      <c r="H140" t="s">
+        <v>70</v>
+      </c>
+      <c r="I140" t="s">
+        <v>23</v>
+      </c>
+      <c r="J140" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10">
+      <c r="A141">
+        <v>100137</v>
+      </c>
+      <c r="B141" s="4">
+        <v>10099</v>
+      </c>
+      <c r="C141" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D141" s="5">
+        <v>2012002</v>
+      </c>
+      <c r="E141" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="F141">
+        <v>9000</v>
+      </c>
+      <c r="G141" t="s">
+        <v>21</v>
+      </c>
+      <c r="H141" t="s">
+        <v>70</v>
+      </c>
+      <c r="I141" t="s">
+        <v>23</v>
+      </c>
+      <c r="J141" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10">
+      <c r="A142">
+        <v>100138</v>
+      </c>
+      <c r="B142" s="4">
+        <v>10099</v>
+      </c>
+      <c r="C142" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D142" s="5">
+        <v>2012003</v>
+      </c>
+      <c r="E142" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="F142">
+        <v>9000</v>
+      </c>
+      <c r="G142" t="s">
+        <v>21</v>
+      </c>
+      <c r="H142" t="s">
+        <v>70</v>
+      </c>
+      <c r="I142" t="s">
+        <v>23</v>
+      </c>
+      <c r="J142" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10">
+      <c r="A143">
+        <v>100139</v>
+      </c>
+      <c r="B143" s="4">
+        <v>10075</v>
+      </c>
+      <c r="C143" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D143" s="5">
+        <v>2012001</v>
+      </c>
+      <c r="E143" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="F143">
+        <v>7000</v>
+      </c>
+      <c r="G143" t="s">
+        <v>28</v>
+      </c>
+      <c r="H143" t="s">
+        <v>70</v>
+      </c>
+      <c r="I143" t="s">
+        <v>23</v>
+      </c>
+      <c r="J143" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10">
+      <c r="A144">
+        <v>100140</v>
+      </c>
+      <c r="B144" s="4">
+        <v>10075</v>
+      </c>
+      <c r="C144" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D144" s="5">
+        <v>2012002</v>
+      </c>
+      <c r="E144" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="F144">
+        <v>7000</v>
+      </c>
+      <c r="G144" t="s">
+        <v>28</v>
+      </c>
+      <c r="H144" t="s">
+        <v>70</v>
+      </c>
+      <c r="I144" t="s">
+        <v>23</v>
+      </c>
+      <c r="J144" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10">
+      <c r="A145">
+        <v>100141</v>
+      </c>
+      <c r="B145" s="4">
+        <v>10075</v>
+      </c>
+      <c r="C145" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D145" s="5">
+        <v>2012003</v>
+      </c>
+      <c r="E145" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="F145">
+        <v>7000</v>
+      </c>
+      <c r="G145" t="s">
+        <v>28</v>
+      </c>
+      <c r="H145" t="s">
+        <v>70</v>
+      </c>
+      <c r="I145" t="s">
+        <v>23</v>
+      </c>
+      <c r="J145" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10">
+      <c r="A146">
+        <v>100142</v>
+      </c>
+      <c r="B146" s="4">
+        <v>10050</v>
+      </c>
+      <c r="C146" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D146" s="5">
+        <v>2012001</v>
+      </c>
+      <c r="E146" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="F146">
+        <v>5000</v>
+      </c>
+      <c r="G146" t="s">
+        <v>31</v>
+      </c>
+      <c r="H146" t="s">
+        <v>70</v>
+      </c>
+      <c r="I146" t="s">
+        <v>23</v>
+      </c>
+      <c r="J146" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10">
+      <c r="A147">
+        <v>100143</v>
+      </c>
+      <c r="B147" s="4">
+        <v>10050</v>
+      </c>
+      <c r="C147" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D147" s="5">
+        <v>2012002</v>
+      </c>
+      <c r="E147" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="F147">
+        <v>5000</v>
+      </c>
+      <c r="G147" t="s">
+        <v>31</v>
+      </c>
+      <c r="H147" t="s">
+        <v>70</v>
+      </c>
+      <c r="I147" t="s">
+        <v>23</v>
+      </c>
+      <c r="J147" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10">
+      <c r="A148">
+        <v>100144</v>
+      </c>
+      <c r="B148" s="4">
+        <v>10050</v>
+      </c>
+      <c r="C148" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D148" s="5">
+        <v>2012003</v>
+      </c>
+      <c r="E148" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="F148">
+        <v>5000</v>
+      </c>
+      <c r="G148" t="s">
+        <v>31</v>
+      </c>
+      <c r="H148" t="s">
+        <v>70</v>
+      </c>
+      <c r="I148" t="s">
+        <v>23</v>
+      </c>
+      <c r="J148" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10">
+      <c r="A149">
+        <v>100145</v>
+      </c>
+      <c r="B149" s="4">
+        <v>10025</v>
+      </c>
+      <c r="C149" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D149" s="5">
+        <v>2012001</v>
+      </c>
+      <c r="E149" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="F149">
+        <v>4000</v>
+      </c>
+      <c r="G149" t="s">
+        <v>34</v>
+      </c>
+      <c r="H149" t="s">
+        <v>70</v>
+      </c>
+      <c r="I149" t="s">
+        <v>23</v>
+      </c>
+      <c r="J149" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10">
+      <c r="A150">
+        <v>100146</v>
+      </c>
+      <c r="B150" s="4">
+        <v>10025</v>
+      </c>
+      <c r="C150" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D150" s="5">
+        <v>2012002</v>
+      </c>
+      <c r="E150" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="F150">
+        <v>4000</v>
+      </c>
+      <c r="G150" t="s">
+        <v>34</v>
+      </c>
+      <c r="H150" t="s">
+        <v>70</v>
+      </c>
+      <c r="I150" t="s">
+        <v>23</v>
+      </c>
+      <c r="J150" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10">
+      <c r="A151">
+        <v>100147</v>
+      </c>
+      <c r="B151" s="4">
+        <v>10025</v>
+      </c>
+      <c r="C151" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D151" s="5">
+        <v>2012003</v>
+      </c>
+      <c r="E151" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="F151">
+        <v>4000</v>
+      </c>
+      <c r="G151" t="s">
+        <v>34</v>
+      </c>
+      <c r="H151" t="s">
+        <v>70</v>
+      </c>
+      <c r="I151" t="s">
+        <v>23</v>
+      </c>
+      <c r="J151" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10">
+      <c r="A152">
+        <v>100148</v>
+      </c>
+      <c r="B152" s="4">
+        <v>10001</v>
+      </c>
+      <c r="C152" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D152" s="5">
+        <v>2012001</v>
+      </c>
+      <c r="E152" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="F152">
+        <v>2000</v>
+      </c>
+      <c r="G152" t="s">
+        <v>36</v>
+      </c>
+      <c r="H152" t="s">
+        <v>70</v>
+      </c>
+      <c r="I152" t="s">
+        <v>23</v>
+      </c>
+      <c r="J152" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10">
+      <c r="A153">
+        <v>100149</v>
+      </c>
+      <c r="B153" s="4">
+        <v>10001</v>
+      </c>
+      <c r="C153" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D153" s="5">
+        <v>2012002</v>
+      </c>
+      <c r="E153" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="F153">
+        <v>2000</v>
+      </c>
+      <c r="G153" t="s">
+        <v>36</v>
+      </c>
+      <c r="H153" t="s">
+        <v>70</v>
+      </c>
+      <c r="I153" t="s">
+        <v>23</v>
+      </c>
+      <c r="J153" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10">
+      <c r="A154">
+        <v>100150</v>
+      </c>
+      <c r="B154" s="4">
+        <v>10001</v>
+      </c>
+      <c r="C154" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D154" s="5">
+        <v>2012003</v>
+      </c>
+      <c r="E154" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="F154">
+        <v>2000</v>
+      </c>
+      <c r="G154" t="s">
+        <v>36</v>
+      </c>
+      <c r="H154" t="s">
+        <v>70</v>
+      </c>
+      <c r="I154" t="s">
+        <v>23</v>
+      </c>
+      <c r="J154" t="s">
         <v>32</v>
       </c>
     </row>
